--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_ending5(2).xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_ending5(2).xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="20385" windowHeight="10605"/>
   </bookViews>
   <sheets>
     <sheet name="圣诺汀之梦_结局5（中）" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1053" uniqueCount="420">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1053" uniqueCount="423">
   <si>
     <t>ID</t>
   </si>
@@ -99,6 +99,9 @@
     <t>他二话不说便扑了上去，但克拉克的子弹却比他更快，子弹从一个刁钻的角度结结实实打在他的右侧大腿上。这一枪破坏了他的平衡，破坏的他的行动能力，也破坏了他和那颗心脏之间最后的一小段距离。</t>
   </si>
   <si>
+    <t>4 enhanced leberch-spooky-piano</t>
+  </si>
+  <si>
     <t>源类型=type:txt_pb; 层级=1</t>
   </si>
   <si>
@@ -258,6 +261,9 @@
     <t>干得好，大卫。</t>
   </si>
   <si>
+    <t>17 enhanced_suspense-tense-background-music</t>
+  </si>
+  <si>
     <t>bgfade(sntzm_gy(ns2)_82,1)</t>
   </si>
   <si>
@@ -528,7 +534,10 @@
     <t>你们走出医院大门。外面是夜风，是泥土和青草的味道，是远处树梢上偶尔掠过的鸟鸣声。那种重新呼吸到新鲜空气的感觉是那样的好，好到让你贪婪的肺部忍不住多吸了两口。</t>
   </si>
   <si>
-    <t>bgfade(sntzm_ending5(2)_45,1)</t>
+    <t>22 the_mountain-horror</t>
+  </si>
+  <si>
+    <t>bgfade(sntzm_ending5(2)_45,1)&amp;unlockmusic(Music22)</t>
   </si>
   <si>
     <t>源类型=type:txt_pb; 层级=44</t>
@@ -2633,7 +2642,7 @@
         <v>15</v>
       </c>
       <c r="I3" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="J3" t="s">
         <v>15</v>
@@ -2642,12 +2651,12 @@
         <v>15</v>
       </c>
       <c r="L3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" ht="54" spans="1:12">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B4" t="s">
         <v>13</v>
@@ -2665,7 +2674,7 @@
         <v>15</v>
       </c>
       <c r="G4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H4" t="s">
         <v>15</v>
@@ -2680,12 +2689,12 @@
         <v>15</v>
       </c>
       <c r="L4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" ht="40.5" spans="1:12">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B5" t="s">
         <v>13</v>
@@ -2703,7 +2712,7 @@
         <v>15</v>
       </c>
       <c r="G5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H5" t="s">
         <v>15</v>
@@ -2715,15 +2724,15 @@
         <v>15</v>
       </c>
       <c r="K5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" ht="40.5" spans="1:12">
       <c r="A6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B6" t="s">
         <v>13</v>
@@ -2741,7 +2750,7 @@
         <v>15</v>
       </c>
       <c r="G6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H6" t="s">
         <v>15</v>
@@ -2756,12 +2765,12 @@
         <v>15</v>
       </c>
       <c r="L6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" ht="27" spans="1:12">
       <c r="A7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B7" t="s">
         <v>13</v>
@@ -2779,7 +2788,7 @@
         <v>15</v>
       </c>
       <c r="G7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H7" t="s">
         <v>15</v>
@@ -2794,12 +2803,12 @@
         <v>15</v>
       </c>
       <c r="L7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" ht="55.5" spans="1:12">
       <c r="A8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B8" t="s">
         <v>13</v>
@@ -2817,7 +2826,7 @@
         <v>15</v>
       </c>
       <c r="G8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H8" t="s">
         <v>15</v>
@@ -2832,12 +2841,12 @@
         <v>15</v>
       </c>
       <c r="L8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9" ht="40.5" spans="1:12">
       <c r="A9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B9" t="s">
         <v>13</v>
@@ -2855,7 +2864,7 @@
         <v>15</v>
       </c>
       <c r="G9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H9" t="s">
         <v>15</v>
@@ -2870,12 +2879,12 @@
         <v>15</v>
       </c>
       <c r="L9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10" ht="27" spans="1:12">
       <c r="A10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B10" t="s">
         <v>13</v>
@@ -2893,7 +2902,7 @@
         <v>15</v>
       </c>
       <c r="G10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H10" t="s">
         <v>15</v>
@@ -2908,12 +2917,12 @@
         <v>15</v>
       </c>
       <c r="L10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" ht="40.5" spans="1:12">
       <c r="A11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B11" t="s">
         <v>13</v>
@@ -2931,7 +2940,7 @@
         <v>15</v>
       </c>
       <c r="G11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H11" t="s">
         <v>15</v>
@@ -2946,12 +2955,12 @@
         <v>15</v>
       </c>
       <c r="L11" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12" ht="67.5" spans="1:12">
       <c r="A12" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B12" t="s">
         <v>13</v>
@@ -2969,7 +2978,7 @@
         <v>15</v>
       </c>
       <c r="G12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H12" t="s">
         <v>15</v>
@@ -2984,12 +2993,12 @@
         <v>15</v>
       </c>
       <c r="L12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" ht="54" spans="1:12">
       <c r="A13" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B13" t="s">
         <v>13</v>
@@ -3007,7 +3016,7 @@
         <v>15</v>
       </c>
       <c r="G13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H13" t="s">
         <v>15</v>
@@ -3019,18 +3028,18 @@
         <v>15</v>
       </c>
       <c r="K13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="L13" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14" spans="1:12">
       <c r="A14" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C14" t="s">
         <v>14</v>
@@ -3045,7 +3054,7 @@
         <v>15</v>
       </c>
       <c r="G14" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H14" t="s">
         <v>15</v>
@@ -3060,12 +3069,12 @@
         <v>15</v>
       </c>
       <c r="L14" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15" ht="40.5" spans="1:12">
       <c r="A15" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B15" t="s">
         <v>13</v>
@@ -3083,7 +3092,7 @@
         <v>15</v>
       </c>
       <c r="G15" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H15" t="s">
         <v>15</v>
@@ -3095,15 +3104,15 @@
         <v>15</v>
       </c>
       <c r="K15" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="L15" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16" ht="67.5" spans="1:12">
       <c r="A16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B16" t="s">
         <v>13</v>
@@ -3121,7 +3130,7 @@
         <v>15</v>
       </c>
       <c r="G16" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H16" t="s">
         <v>15</v>
@@ -3136,12 +3145,12 @@
         <v>15</v>
       </c>
       <c r="L16" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17" ht="40.5" spans="1:12">
       <c r="A17" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B17" t="s">
         <v>13</v>
@@ -3159,7 +3168,7 @@
         <v>15</v>
       </c>
       <c r="G17" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H17" t="s">
         <v>15</v>
@@ -3174,12 +3183,12 @@
         <v>15</v>
       </c>
       <c r="L17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="18" ht="40.5" spans="1:12">
       <c r="A18" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B18" t="s">
         <v>13</v>
@@ -3197,7 +3206,7 @@
         <v>15</v>
       </c>
       <c r="G18" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H18" t="s">
         <v>15</v>
@@ -3209,15 +3218,15 @@
         <v>15</v>
       </c>
       <c r="L18" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="19" ht="60" spans="1:12">
       <c r="A19" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B19" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C19" t="s">
         <v>14</v>
@@ -3232,27 +3241,27 @@
         <v>15</v>
       </c>
       <c r="G19" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H19" t="s">
         <v>15</v>
       </c>
       <c r="I19" t="s">
-        <v>15</v>
+        <v>75</v>
       </c>
       <c r="J19" t="s">
         <v>15</v>
       </c>
       <c r="K19" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L19" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="20" ht="40.5" spans="1:12">
       <c r="A20" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B20" t="s">
         <v>13</v>
@@ -3270,7 +3279,7 @@
         <v>15</v>
       </c>
       <c r="G20" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H20" t="s">
         <v>15</v>
@@ -3285,12 +3294,12 @@
         <v>15</v>
       </c>
       <c r="L20" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="21" ht="54" spans="1:12">
       <c r="A21" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B21" t="s">
         <v>13</v>
@@ -3308,7 +3317,7 @@
         <v>15</v>
       </c>
       <c r="G21" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H21" t="s">
         <v>15</v>
@@ -3323,12 +3332,12 @@
         <v>15</v>
       </c>
       <c r="L21" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="22" ht="40.5" spans="1:12">
       <c r="A22" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B22" t="s">
         <v>13</v>
@@ -3346,7 +3355,7 @@
         <v>15</v>
       </c>
       <c r="G22" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H22" t="s">
         <v>15</v>
@@ -3361,21 +3370,21 @@
         <v>15</v>
       </c>
       <c r="L22" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="23" spans="1:12">
       <c r="A23" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B23" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C23" t="s">
         <v>14</v>
       </c>
       <c r="D23" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E23" t="s">
         <v>15</v>
@@ -3384,7 +3393,7 @@
         <v>15</v>
       </c>
       <c r="G23" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H23" t="s">
         <v>15</v>
@@ -3396,24 +3405,24 @@
         <v>15</v>
       </c>
       <c r="K23" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="L23" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="24" ht="67.5" spans="1:12">
       <c r="A24" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B24" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C24" t="s">
         <v>14</v>
       </c>
       <c r="D24" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E24" t="s">
         <v>15</v>
@@ -3422,7 +3431,7 @@
         <v>15</v>
       </c>
       <c r="G24" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H24" t="s">
         <v>15</v>
@@ -3437,12 +3446,12 @@
         <v>15</v>
       </c>
       <c r="L24" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="25" ht="27" spans="1:12">
       <c r="A25" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B25" t="s">
         <v>13</v>
@@ -3451,7 +3460,7 @@
         <v>14</v>
       </c>
       <c r="D25" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E25" t="s">
         <v>15</v>
@@ -3460,7 +3469,7 @@
         <v>15</v>
       </c>
       <c r="G25" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="H25" t="s">
         <v>15</v>
@@ -3472,24 +3481,24 @@
         <v>15</v>
       </c>
       <c r="K25" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L25" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="26" ht="40.5" spans="1:12">
       <c r="A26" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B26" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C26" t="s">
         <v>14</v>
       </c>
       <c r="D26" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E26" t="s">
         <v>15</v>
@@ -3498,7 +3507,7 @@
         <v>15</v>
       </c>
       <c r="G26" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H26" t="s">
         <v>15</v>
@@ -3510,15 +3519,15 @@
         <v>15</v>
       </c>
       <c r="K26" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="L26" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="27" ht="27" spans="1:12">
       <c r="A27" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B27" t="s">
         <v>13</v>
@@ -3527,7 +3536,7 @@
         <v>14</v>
       </c>
       <c r="D27" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E27" t="s">
         <v>15</v>
@@ -3536,7 +3545,7 @@
         <v>15</v>
       </c>
       <c r="G27" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="H27" t="s">
         <v>15</v>
@@ -3551,21 +3560,21 @@
         <v>15</v>
       </c>
       <c r="L27" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="28" ht="54" spans="1:12">
       <c r="A28" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B28" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C28" t="s">
         <v>14</v>
       </c>
       <c r="D28" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E28" t="s">
         <v>15</v>
@@ -3574,7 +3583,7 @@
         <v>15</v>
       </c>
       <c r="G28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="H28" t="s">
         <v>15</v>
@@ -3589,12 +3598,12 @@
         <v>15</v>
       </c>
       <c r="L28" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="29" ht="27" spans="1:12">
       <c r="A29" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B29" t="s">
         <v>13</v>
@@ -3603,7 +3612,7 @@
         <v>14</v>
       </c>
       <c r="D29" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E29" t="s">
         <v>15</v>
@@ -3612,7 +3621,7 @@
         <v>15</v>
       </c>
       <c r="G29" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="H29" t="s">
         <v>15</v>
@@ -3624,15 +3633,15 @@
         <v>15</v>
       </c>
       <c r="K29" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L29" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="30" ht="55.5" spans="1:12">
       <c r="A30" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B30" t="s">
         <v>13</v>
@@ -3650,7 +3659,7 @@
         <v>15</v>
       </c>
       <c r="G30" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H30" t="s">
         <v>15</v>
@@ -3662,15 +3671,15 @@
         <v>15</v>
       </c>
       <c r="K30" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="L30" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="31" ht="55.5" spans="1:12">
       <c r="A31" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B31" t="s">
         <v>13</v>
@@ -3688,7 +3697,7 @@
         <v>15</v>
       </c>
       <c r="G31" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="H31" t="s">
         <v>15</v>
@@ -3703,12 +3712,12 @@
         <v>15</v>
       </c>
       <c r="L31" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="32" ht="28.5" spans="1:12">
       <c r="A32" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B32" t="s">
         <v>13</v>
@@ -3726,7 +3735,7 @@
         <v>15</v>
       </c>
       <c r="G32" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H32" t="s">
         <v>15</v>
@@ -3741,21 +3750,21 @@
         <v>15</v>
       </c>
       <c r="L32" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="33" ht="27" spans="1:12">
       <c r="A33" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B33" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C33" t="s">
         <v>14</v>
       </c>
       <c r="D33" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E33" t="s">
         <v>15</v>
@@ -3764,7 +3773,7 @@
         <v>15</v>
       </c>
       <c r="G33" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H33" t="s">
         <v>15</v>
@@ -3776,15 +3785,15 @@
         <v>15</v>
       </c>
       <c r="K33" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="L33" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="34" ht="40.5" spans="1:12">
       <c r="A34" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B34" t="s">
         <v>13</v>
@@ -3793,7 +3802,7 @@
         <v>14</v>
       </c>
       <c r="D34" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E34" t="s">
         <v>15</v>
@@ -3802,7 +3811,7 @@
         <v>15</v>
       </c>
       <c r="G34" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="H34" t="s">
         <v>15</v>
@@ -3814,15 +3823,15 @@
         <v>15</v>
       </c>
       <c r="K34" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L34" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="35" ht="55.5" spans="1:12">
       <c r="A35" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B35" t="s">
         <v>13</v>
@@ -3840,7 +3849,7 @@
         <v>15</v>
       </c>
       <c r="G35" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="H35" t="s">
         <v>15</v>
@@ -3855,12 +3864,12 @@
         <v>15</v>
       </c>
       <c r="L35" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="36" ht="55.5" spans="1:12">
       <c r="A36" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B36" t="s">
         <v>13</v>
@@ -3878,7 +3887,7 @@
         <v>15</v>
       </c>
       <c r="G36" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H36" t="s">
         <v>15</v>
@@ -3893,12 +3902,12 @@
         <v>15</v>
       </c>
       <c r="L36" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="37" ht="55.5" spans="1:12">
       <c r="A37" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B37" t="s">
         <v>13</v>
@@ -3916,7 +3925,7 @@
         <v>15</v>
       </c>
       <c r="G37" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H37" t="s">
         <v>15</v>
@@ -3931,12 +3940,12 @@
         <v>15</v>
       </c>
       <c r="L37" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="38" ht="43.5" spans="1:12">
       <c r="A38" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B38" t="s">
         <v>13</v>
@@ -3954,7 +3963,7 @@
         <v>15</v>
       </c>
       <c r="G38" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H38" t="s">
         <v>15</v>
@@ -3966,15 +3975,15 @@
         <v>15</v>
       </c>
       <c r="K38" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="L38" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="39" ht="67.5" spans="1:12">
       <c r="A39" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B39" t="s">
         <v>13</v>
@@ -3992,7 +4001,7 @@
         <v>15</v>
       </c>
       <c r="G39" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H39" t="s">
         <v>15</v>
@@ -4007,12 +4016,12 @@
         <v>15</v>
       </c>
       <c r="L39" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="40" ht="67.5" spans="1:12">
       <c r="A40" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B40" t="s">
         <v>13</v>
@@ -4030,7 +4039,7 @@
         <v>15</v>
       </c>
       <c r="G40" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H40" t="s">
         <v>15</v>
@@ -4045,12 +4054,12 @@
         <v>15</v>
       </c>
       <c r="L40" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="41" ht="27" spans="1:12">
       <c r="A41" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B41" t="s">
         <v>13</v>
@@ -4068,7 +4077,7 @@
         <v>15</v>
       </c>
       <c r="G41" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H41" t="s">
         <v>15</v>
@@ -4083,12 +4092,12 @@
         <v>15</v>
       </c>
       <c r="L41" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="42" ht="54" spans="1:12">
       <c r="A42" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B42" t="s">
         <v>13</v>
@@ -4106,7 +4115,7 @@
         <v>15</v>
       </c>
       <c r="G42" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="H42" t="s">
         <v>15</v>
@@ -4121,12 +4130,12 @@
         <v>15</v>
       </c>
       <c r="L42" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="43" ht="67.5" spans="1:12">
       <c r="A43" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B43" t="s">
         <v>13</v>
@@ -4144,7 +4153,7 @@
         <v>15</v>
       </c>
       <c r="G43" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="H43" t="s">
         <v>15</v>
@@ -4159,12 +4168,12 @@
         <v>15</v>
       </c>
       <c r="L43" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="44" ht="55.5" spans="1:12">
       <c r="A44" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B44" t="s">
         <v>13</v>
@@ -4182,7 +4191,7 @@
         <v>15</v>
       </c>
       <c r="G44" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="H44" t="s">
         <v>15</v>
@@ -4197,12 +4206,12 @@
         <v>15</v>
       </c>
       <c r="L44" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="45" ht="42" spans="1:12">
       <c r="A45" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B45" t="s">
         <v>13</v>
@@ -4220,7 +4229,7 @@
         <v>15</v>
       </c>
       <c r="G45" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H45" t="s">
         <v>15</v>
@@ -4235,12 +4244,12 @@
         <v>15</v>
       </c>
       <c r="L45" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="46" ht="54" spans="1:12">
       <c r="A46" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B46" t="s">
         <v>13</v>
@@ -4258,27 +4267,27 @@
         <v>15</v>
       </c>
       <c r="G46" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="H46" t="s">
         <v>15</v>
       </c>
       <c r="I46" t="s">
-        <v>15</v>
+        <v>166</v>
       </c>
       <c r="J46" t="s">
         <v>15</v>
       </c>
       <c r="K46" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="L46" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
     </row>
     <row r="47" ht="55.5" spans="1:12">
       <c r="A47" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B47" t="s">
         <v>13</v>
@@ -4296,7 +4305,7 @@
         <v>15</v>
       </c>
       <c r="G47" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="H47" t="s">
         <v>15</v>
@@ -4308,15 +4317,15 @@
         <v>15</v>
       </c>
       <c r="K47" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="L47" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="48" ht="69" spans="1:12">
       <c r="A48" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B48" t="s">
         <v>13</v>
@@ -4334,7 +4343,7 @@
         <v>15</v>
       </c>
       <c r="G48" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="H48" t="s">
         <v>15</v>
@@ -4349,12 +4358,12 @@
         <v>15</v>
       </c>
       <c r="L48" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="49" ht="40.5" spans="1:12">
       <c r="A49" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B49" t="s">
         <v>13</v>
@@ -4372,7 +4381,7 @@
         <v>15</v>
       </c>
       <c r="G49" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="H49" t="s">
         <v>15</v>
@@ -4387,12 +4396,12 @@
         <v>15</v>
       </c>
       <c r="L49" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
     </row>
     <row r="50" ht="54" spans="1:12">
       <c r="A50" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B50" t="s">
         <v>13</v>
@@ -4410,7 +4419,7 @@
         <v>15</v>
       </c>
       <c r="G50" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="H50" t="s">
         <v>15</v>
@@ -4425,12 +4434,12 @@
         <v>15</v>
       </c>
       <c r="L50" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
     </row>
     <row r="51" ht="42" spans="1:12">
       <c r="A51" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B51" t="s">
         <v>13</v>
@@ -4448,7 +4457,7 @@
         <v>15</v>
       </c>
       <c r="G51" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="H51" t="s">
         <v>15</v>
@@ -4463,12 +4472,12 @@
         <v>15</v>
       </c>
       <c r="L51" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="52" spans="1:12">
       <c r="A52" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B52" t="s">
         <v>13</v>
@@ -4486,7 +4495,7 @@
         <v>15</v>
       </c>
       <c r="G52" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="H52" t="s">
         <v>15</v>
@@ -4501,12 +4510,12 @@
         <v>15</v>
       </c>
       <c r="L52" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="53" ht="27" spans="1:12">
       <c r="A53" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B53" t="s">
         <v>13</v>
@@ -4524,7 +4533,7 @@
         <v>15</v>
       </c>
       <c r="G53" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="H53" t="s">
         <v>15</v>
@@ -4539,12 +4548,12 @@
         <v>15</v>
       </c>
       <c r="L53" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="54" ht="30" spans="1:12">
       <c r="A54" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="B54" t="s">
         <v>13</v>
@@ -4562,7 +4571,7 @@
         <v>15</v>
       </c>
       <c r="G54" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="H54" t="s">
         <v>15</v>
@@ -4577,15 +4586,15 @@
         <v>15</v>
       </c>
       <c r="L54" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
     </row>
     <row r="55" spans="1:12">
       <c r="A55" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B55" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C55" t="s">
         <v>14</v>
@@ -4600,7 +4609,7 @@
         <v>15</v>
       </c>
       <c r="G55" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="H55" t="s">
         <v>15</v>
@@ -4615,12 +4624,12 @@
         <v>15</v>
       </c>
       <c r="L55" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="56" spans="1:12">
       <c r="A56" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B56" t="s">
         <v>13</v>
@@ -4638,7 +4647,7 @@
         <v>15</v>
       </c>
       <c r="G56" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="H56" t="s">
         <v>15</v>
@@ -4653,15 +4662,15 @@
         <v>15</v>
       </c>
       <c r="L56" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="57" ht="27" spans="1:12">
       <c r="A57" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="B57" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C57" t="s">
         <v>14</v>
@@ -4676,7 +4685,7 @@
         <v>15</v>
       </c>
       <c r="G57" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="H57" t="s">
         <v>15</v>
@@ -4691,12 +4700,12 @@
         <v>15</v>
       </c>
       <c r="L57" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
     </row>
     <row r="58" spans="1:12">
       <c r="A58" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B58" t="s">
         <v>13</v>
@@ -4714,7 +4723,7 @@
         <v>15</v>
       </c>
       <c r="G58" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="H58" t="s">
         <v>15</v>
@@ -4729,12 +4738,12 @@
         <v>15</v>
       </c>
       <c r="L58" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
     </row>
     <row r="59" spans="1:12">
       <c r="A59" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B59" t="s">
         <v>13</v>
@@ -4752,7 +4761,7 @@
         <v>15</v>
       </c>
       <c r="G59" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="H59" t="s">
         <v>15</v>
@@ -4767,12 +4776,12 @@
         <v>15</v>
       </c>
       <c r="L59" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
     </row>
     <row r="60" ht="57" spans="1:12">
       <c r="A60" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B60" t="s">
         <v>13</v>
@@ -4790,7 +4799,7 @@
         <v>15</v>
       </c>
       <c r="G60" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="H60" t="s">
         <v>15</v>
@@ -4805,12 +4814,12 @@
         <v>15</v>
       </c>
       <c r="L60" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
     </row>
     <row r="61" ht="40.5" spans="1:12">
       <c r="A61" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B61" t="s">
         <v>13</v>
@@ -4828,7 +4837,7 @@
         <v>15</v>
       </c>
       <c r="G61" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="H61" t="s">
         <v>15</v>
@@ -4843,12 +4852,12 @@
         <v>15</v>
       </c>
       <c r="L61" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
     </row>
     <row r="62" ht="40.5" spans="1:12">
       <c r="A62" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B62" t="s">
         <v>13</v>
@@ -4866,7 +4875,7 @@
         <v>15</v>
       </c>
       <c r="G62" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="H62" t="s">
         <v>15</v>
@@ -4878,15 +4887,15 @@
         <v>15</v>
       </c>
       <c r="K62" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="L62" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
     </row>
     <row r="63" ht="27" spans="1:12">
       <c r="A63" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="B63" t="s">
         <v>13</v>
@@ -4904,7 +4913,7 @@
         <v>15</v>
       </c>
       <c r="G63" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="H63" t="s">
         <v>15</v>
@@ -4916,18 +4925,18 @@
         <v>15</v>
       </c>
       <c r="K63" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="L63" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
     </row>
     <row r="64" ht="27" spans="1:12">
       <c r="A64" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="B64" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C64" t="s">
         <v>14</v>
@@ -4942,7 +4951,7 @@
         <v>15</v>
       </c>
       <c r="G64" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="H64" t="s">
         <v>15</v>
@@ -4957,12 +4966,12 @@
         <v>15</v>
       </c>
       <c r="L64" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
     </row>
     <row r="65" spans="1:12">
       <c r="A65" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B65" t="s">
         <v>13</v>
@@ -4980,7 +4989,7 @@
         <v>15</v>
       </c>
       <c r="G65" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="H65" t="s">
         <v>15</v>
@@ -4992,18 +5001,18 @@
         <v>15</v>
       </c>
       <c r="K65" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="L65" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
     </row>
     <row r="66" spans="1:12">
       <c r="A66" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="B66" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C66" t="s">
         <v>14</v>
@@ -5018,7 +5027,7 @@
         <v>15</v>
       </c>
       <c r="G66" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="H66" t="s">
         <v>15</v>
@@ -5033,12 +5042,12 @@
         <v>15</v>
       </c>
       <c r="L66" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="67" ht="54" spans="1:12">
       <c r="A67" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B67" t="s">
         <v>13</v>
@@ -5056,7 +5065,7 @@
         <v>15</v>
       </c>
       <c r="G67" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="H67" t="s">
         <v>15</v>
@@ -5071,15 +5080,15 @@
         <v>15</v>
       </c>
       <c r="L67" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="68" spans="1:12">
       <c r="A68" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B68" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C68" t="s">
         <v>14</v>
@@ -5094,7 +5103,7 @@
         <v>15</v>
       </c>
       <c r="G68" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="H68" t="s">
         <v>15</v>
@@ -5109,12 +5118,12 @@
         <v>15</v>
       </c>
       <c r="L68" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
     </row>
     <row r="69" ht="27" spans="1:12">
       <c r="A69" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="B69" t="s">
         <v>13</v>
@@ -5132,7 +5141,7 @@
         <v>15</v>
       </c>
       <c r="G69" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="H69" t="s">
         <v>15</v>
@@ -5147,12 +5156,12 @@
         <v>15</v>
       </c>
       <c r="L69" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
     </row>
     <row r="70" ht="43.5" spans="1:12">
       <c r="A70" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="B70" t="s">
         <v>13</v>
@@ -5170,7 +5179,7 @@
         <v>15</v>
       </c>
       <c r="G70" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="H70" t="s">
         <v>15</v>
@@ -5182,10 +5191,10 @@
         <v>15</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="L70" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
     </row>
   </sheetData>
@@ -5206,47 +5215,47 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
     </row>
     <row r="2" ht="30" spans="1:2">
       <c r="A2" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="B2" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B3" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="B4" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="B5" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="B6" t="s">
         <v>12</v>
@@ -5254,7 +5263,7 @@
     </row>
     <row r="7" ht="27" spans="1:2">
       <c r="A7" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
@@ -5262,66 +5271,66 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="B8" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="9" ht="27" spans="1:2">
       <c r="A9" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="B9" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10" ht="75" spans="1:2">
       <c r="A10" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="B10" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
     </row>
     <row r="11" ht="75" spans="1:2">
       <c r="A11" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="B11" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
     </row>
     <row r="12" ht="57" spans="1:2">
       <c r="A12" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="B12" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:2">
       <c r="A13" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="B13" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
     </row>
     <row r="14" ht="105" spans="1:2">
       <c r="A14" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="B14" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="15" ht="75" spans="1:2">
       <c r="A15" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="B15" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
     </row>
   </sheetData>
@@ -5343,616 +5352,616 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="2" ht="73.5" spans="1:6">
       <c r="A2" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B2" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="C2" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="D2" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="E2" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="F2" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="3" ht="103.5" spans="1:6">
       <c r="A3" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B3" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C3" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="D3" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="E3" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="F3" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="4" ht="45" spans="1:6">
       <c r="A4" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B4" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="C4" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="D4" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="E4" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="F4" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="5" ht="45" spans="1:6">
       <c r="A5" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B5" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="C5" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="D5" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="E5" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F5" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="6" ht="45" spans="1:6">
       <c r="A6" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B6" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="C6" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="D6" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="E6" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="F6" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="7" ht="75" spans="1:6">
       <c r="A7" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B7" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="C7" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="D7" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="E7" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="F7" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="8" ht="45" spans="1:6">
       <c r="A8" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="B8" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="C8" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="D8" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="E8" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="F8" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="9" ht="45" spans="1:6">
       <c r="A9" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="B9" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="C9" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="D9" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="E9" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="F9" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10" ht="58.5" spans="1:6">
       <c r="A10" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="B10" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="C10" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="D10" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="E10" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="F10" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="11" ht="60" spans="1:6">
       <c r="A11" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="B11" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="C11" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="D11" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="E11" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="F11" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="12" ht="58.5" spans="1:6">
       <c r="A12" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="B12" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="C12" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="D12" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="E12" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="F12" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:6">
       <c r="A13" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="B13" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="C13" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D13" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="E13" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="F13" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="14" ht="58.5" spans="1:6">
       <c r="A14" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="B14" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="C14" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="D14" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="E14" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="F14" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="15" ht="58.5" spans="1:6">
       <c r="A15" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="B15" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="C15" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="D15" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="E15" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="F15" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="16" ht="58.5" spans="1:6">
       <c r="A16" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="B16" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="C16" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="D16" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="E16" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="F16" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="17" ht="58.5" spans="1:6">
       <c r="A17" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="B17" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="C17" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="D17" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="E17" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="F17" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="18" ht="58.5" spans="1:6">
       <c r="A18" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="B18" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="C18" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="D18" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="E18" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="F18" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="19" ht="58.5" spans="1:6">
       <c r="A19" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="B19" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="C19" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="D19" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="E19" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="F19" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="20" ht="72" spans="1:6">
       <c r="A20" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="B20" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="C20" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="D20" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="E20" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="F20" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="21" ht="58.5" spans="1:6">
       <c r="A21" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="B21" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="C21" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="D21" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="E21" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="F21" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="22" ht="58.5" spans="1:6">
       <c r="A22" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="B22" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="C22" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="D22" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="E22" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="F22" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
     <row r="23" ht="58.5" spans="1:6">
       <c r="A23" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="B23" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="C23" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="D23" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="E23" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="F23" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="24" ht="58.5" spans="1:6">
       <c r="A24" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="B24" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="C24" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="D24" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="E24" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="F24" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="25" ht="90" spans="1:6">
       <c r="A25" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="B25" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="C25" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="D25" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="E25" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="F25" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="26" ht="58.5" spans="1:6">
       <c r="A26" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="B26" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="C26" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="D26" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="E26" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="F26" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="27" ht="58.5" spans="1:6">
       <c r="A27" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="B27" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="C27" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="D27" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="E27" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="F27" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="28" ht="58.5" spans="1:6">
       <c r="A28" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="B28" t="s">
+        <v>405</v>
+      </c>
+      <c r="C28" t="s">
+        <v>406</v>
+      </c>
+      <c r="D28" t="s">
         <v>402</v>
       </c>
-      <c r="C28" t="s">
-        <v>403</v>
-      </c>
-      <c r="D28" t="s">
-        <v>399</v>
-      </c>
       <c r="E28" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="F28" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="29" ht="73.5" spans="1:6">
       <c r="A29" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="B29" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="C29" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="D29" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="E29" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="F29" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
     <row r="30" ht="58.5" spans="1:6">
       <c r="A30" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="B30" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C30" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="D30" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="E30" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F30" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="B31" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="C31" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="D31" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
   </sheetData>
